--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N118_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N118_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.31997557338165</v>
+        <v>1.676996030674518</v>
       </c>
       <c r="D2" t="n">
-        <v>62.8086141196744</v>
+        <v>10.20639979444709</v>
       </c>
       <c r="E2" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F2" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.39987176221457</v>
+        <v>3.152479161359868</v>
       </c>
       <c r="D3" t="n">
-        <v>59.21915903074426</v>
+        <v>9.623113342495943</v>
       </c>
       <c r="E3" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F3" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.12519520262295</v>
+        <v>7.332844220426229</v>
       </c>
       <c r="D4" t="n">
-        <v>34.13857047683285</v>
+        <v>5.547517702485339</v>
       </c>
       <c r="E4" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F4" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.86811552975797</v>
+        <v>7.941068773585671</v>
       </c>
       <c r="D5" t="n">
-        <v>49.67347574867996</v>
+        <v>8.071939809160494</v>
       </c>
       <c r="E5" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F5" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>55.70780509377288</v>
+        <v>9.052518327738092</v>
       </c>
       <c r="D6" t="n">
-        <v>46.33484012176542</v>
+        <v>7.529411519786881</v>
       </c>
       <c r="E6" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F6" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.03904248315763</v>
+        <v>2.931344403513116</v>
       </c>
       <c r="D7" t="n">
-        <v>4.565886304957735</v>
+        <v>0.741956524555632</v>
       </c>
       <c r="E7" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F7" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>56.23266837689867</v>
+        <v>9.137808611246033</v>
       </c>
       <c r="D8" t="n">
-        <v>50.92059056442589</v>
+        <v>8.274595966719207</v>
       </c>
       <c r="E8" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F8" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>49.99721566239303</v>
+        <v>8.124547545138867</v>
       </c>
       <c r="D9" t="n">
-        <v>47.28072291390266</v>
+        <v>7.683117473509182</v>
       </c>
       <c r="E9" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F9" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.91670955313245</v>
+        <v>5.673965302384024</v>
       </c>
       <c r="D10" t="n">
-        <v>36.73085834437699</v>
+        <v>5.968764480961261</v>
       </c>
       <c r="E10" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F10" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.90590598522148</v>
+        <v>2.097209722598491</v>
       </c>
       <c r="D11" t="n">
-        <v>25.5670075136518</v>
+        <v>4.154638720968418</v>
       </c>
       <c r="E11" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F11" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.48781072441155</v>
+        <v>4.466769242716877</v>
       </c>
       <c r="D12" t="n">
-        <v>34.05729999297803</v>
+        <v>5.534311248858931</v>
       </c>
       <c r="E12" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F12" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.70476667256481</v>
+        <v>3.689524584291782</v>
       </c>
       <c r="D13" t="n">
-        <v>34.9504149335555</v>
+        <v>5.679442426702769</v>
       </c>
       <c r="E13" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F13" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>46.61610477911183</v>
+        <v>7.575117026605673</v>
       </c>
       <c r="D14" t="n">
-        <v>57.28788023496107</v>
+        <v>9.309280538181174</v>
       </c>
       <c r="E14" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F14" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>50.39960111768103</v>
+        <v>8.189935181623168</v>
       </c>
       <c r="D15" t="n">
-        <v>63.76786712789161</v>
+        <v>10.36227840828239</v>
       </c>
       <c r="E15" t="n">
-        <v>16.04002305581889</v>
+        <v>2.606503746570571</v>
       </c>
       <c r="F15" t="n">
-        <v>15.74185316233791</v>
+        <v>2.558051138879911</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
